--- a/informe/Estructura_Informe_Conexion.xlsx
+++ b/informe/Estructura_Informe_Conexion.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Estructura_Informe" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Escenarios_8.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Causales_Rechazo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estructura_Informe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenarios_8.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Causales_Rechazo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Estructura_Informe'!$A$1:$F$24</definedName>
@@ -589,7 +589,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Transformador propio documentado (Dyn5, 1250 kVA, 13200/800-462V). Impedancia 6% asumida como valor tipico normalizado, declarado expresamente: falta protocolo de pruebas.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -860,14 +864,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Falta</t>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Solicitar al OR si hay bancos de condensadores/reactores en la zona de influencia</t>
+          <t>EBSA no reporta bancos de condensadores ni reactores en DOC_REF_EST; se modela sin compensacion. Proyecto sin compensacion propia (cos phi=1).</t>
         </is>
       </c>
     </row>
@@ -924,14 +928,14 @@
           <t>Flujo_carga.py + Cortocircuito.py (CasoBase) + calculo manual de verificacion</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>[PENDIENTE REHACER CON GD1/GD2] LIMITACION DOCUMENTADA: EBSA solo da datos de entrada, no resultados propios de tension/cargabilidad/cortocircuito - no se puede hacer la comparacion del 10% que pide 8.1. Se propone en su lugar un analisis estadistico de desviacion CasoBase vs con-GD (pendiente de calcular). Se incluyo metodologia detallada de calculo de corto (cadena de impedancias IEC60909) verificada contra PowerFactory (1.14kA manual vs 1.236kA PowerFactory en P3, ~7% diferencia esperada) - conclusion: la memoria sobreestima el Icc en 800V en ~1.5x (7.49kA red completa vs 11.2kA memoria)</t>
+          <t>Desviacion CasoBase vs con-proyecto: tension +0.235% promedio / +0.623% max; cargabilidad +1.88 pp promedio, concentrada en la linea de evacuacion. Muy por debajo del 10%.</t>
         </is>
       </c>
     </row>
@@ -988,14 +992,14 @@
           <t>Flujo_carga.py (ESCALA_DEMANDA)</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>[BUG DE UNIDADES CORREGIDO EN Flujo_carga.py 2026-09-18 - resultados previos invalidos, falta re-correr] [PENDIENTE REHACER CON GD1/GD2] N-1 NO SE REALIZA: justificado, red radial pura sin caminos alternos, N-1 no aporta informacion en topologia radial. ESCALA_DEMANDA=1.0104 ya implementado en el script para el ano t+x=2028. Falta correr ambas corridas (t y t+x) y consolidar tablas</t>
+          <t>48 escenarios convergieron. U entre 0.9368 y 1.0230 pu (limite 0.90-1.10). Cargabilidad max 80.55%. Sin violaciones.</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1063,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Falta solo la verificacion numerica de la formula Pgen&gt;=Pmin_dem con el Pmin_dem historico del circuito 15344</t>
+          <t>Balance numerico: generacion total 1.650 MW vs demanda minima 5.625 MW -&gt; deficit de 3.975 MW, isla inviable. Mas certificacion anti-isla Intertek.</t>
         </is>
       </c>
     </row>
@@ -1084,14 +1088,14 @@
           <t>Flujo_carga.py</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>[BUG DE UNIDADES CORREGIDO EN Flujo_carga.py 2026-09-18 - resultados previos invalidos, falta re-correr] [PENDIENTE REHACER CON GD1/GD2] Alcance confirmado: perdidas de TODO el sistema (lineas+transformadores), con generador vs sin generador, anos t y t+x. Falta consolidar tabla resumen</t>
+          <t>Perdidas +9.26 kW (2026) / +9.21 kW (2028), concentradas integramente en la linea de evacuacion AL 1.32km. Resto del sistema reduce perdidas.</t>
         </is>
       </c>
     </row>
@@ -1208,14 +1212,14 @@
           <t>scripts/Coordinacion_Protecciones.py</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>COMPROBACION (no EACP completo) implementada y corrida: coordinacion de cabecera 15344 OK, no requiere reajuste (trifasico +1.05%, monofasico +0.13%, ambos siguen en zona instantanea). Metodologia programada (formula IEC 60255-151 Normal Inverse) documentada con formulas en el .tex (seccion Anexo) y en README.md. Aporte de falla del generador (Ikss=0.7146kA) documentado como insumo para malla de puesta a tierra. PENDIENTE: confirmar equipo de corte en MV (13.2kV) del transformador propio, exigido por Anexo 1 Acuerdo 2121 para 0.25-1MW.</t>
+          <t>Comprobacion de cabecera (no requiere reajuste) + definicion completa de la proteccion del PC con ajustes, selectividad 0.406 s y margen anti-isla 1.0 s. Celda con reconectador adoptada.</t>
         </is>
       </c>
     </row>
@@ -1426,14 +1430,14 @@
           <t>No se desarrollan todos los analisis para los anos t y t+x</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Falta correr los scripts para el ano t+x</t>
+          <t>Ambos anos (2026 y 2028) simulados; 48 escenarios convergieron.</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1454,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Certificado Intertek CN-PV-220287 (IEC 61727/62116) + inversor certificado IEEE1547/UL1741/IEC62109 con anti-isla integrado (ver memoria de calculo). Falta solo la verificacion numerica Pgen&gt;=Pmin_dem</t>
+          <t>Certificacion Intertek CN-PV-220287 + balance de potencia (deficit 3.975 MW) + funciones 27/81/81R del PC.</t>
         </is>
       </c>
     </row>
@@ -1470,14 +1474,14 @@
           <t>Se supera la capacidad de corte de interruptores en subestaciones cercanas</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Requiere el dato de capacidad de corte real de los interruptores</t>
+          <t>Maximo 8.164 kA con proyecto vs 10 kA de capacidad de corte declarada por EBSA.</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1496,14 @@
           <t>Nivel de carga en condicion normal &gt; 100% en algun elemento cercano</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Revisar hoja Cargabilidad_% de Resultados_Flujo_Carga.xlsx</t>
+          <t>Maximo 80.55% (transformador del proyecto); linea mas cargada 80.24%.</t>
         </is>
       </c>
     </row>
@@ -1514,14 +1518,14 @@
           <t>Nivel de carga en contingencia N-1 &gt; limite de emergencia</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Falta implementar analisis N-1</t>
+          <t>Topologia radial pura: no hay redistribucion de flujo que evaluar.</t>
         </is>
       </c>
     </row>
@@ -1536,14 +1540,14 @@
           <t>Sobretensiones &gt; 1.1 p.u. en alguna subestacion (N o N-1)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Revisar hoja U_pu de Resultados_Flujo_Carga.xlsx</t>
+          <t>Maximo 1.0230 pu.</t>
         </is>
       </c>
     </row>

--- a/informe/Estructura_Informe_Conexion.xlsx
+++ b/informe/Estructura_Informe_Conexion.xlsx
@@ -740,14 +740,14 @@
           <t>DOC_REF_EST + montaje manual en PowerFactory (decision del usuario, no via script)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>HALLAZGO: existen 2 GD ya conectados al circuito (GD1/GD2, 330kVA c/u en P4/P5_15344) nunca antes modelados. El usuario los monta MANUALMENTE en PowerFactory (no via script). Ficha de caracteristicas genericas en Parametros_Proyecto.xlsx (cosphi=1, despacho=perfil solar propio escalado a 330kW, corto=No Short-Circuit Contribution). REQUIERE volver a correr Flujo_carga.py y Cortocircuito.py una vez montados - todos los resultados previos deben regenerarse</t>
+          <t>GD1/GD2 incorporados al CasoBase con despacho solar propio. Conectados en P5 y P6 15344 (confirmado contra el unifilar). Su efecto: -4.79 kW de perdidas frente a carga pura.</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Desviacion CasoBase vs con-proyecto: tension +0.235% promedio / +0.623% max; cargabilidad +1.88 pp promedio, concentrada en la linea de evacuacion. Muy por debajo del 10%.</t>
+          <t>Desviacion tension +0.129% promedio / +0.616% max; cargabilidad +0.577 pp. Muy por debajo del 10%.</t>
         </is>
       </c>
     </row>
@@ -960,14 +960,14 @@
           <t>Ver hoja 'Escenarios_8.2' - ya se identificaron las horas candidatas cruzando Parametros_Demanda.xlsx con la Tabla 16 de la memoria de calculo</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Falta decidir si la demanda relevante es la agregada (8 cargas) o solo el circuito 15344 (mas preciso para el punto de conexion)</t>
+          <t>Los 3 escenarios simulados: CargaPura (h15), maxima diferencia (h12, generacion 990 kW) y maxima demanda+generacion (h15). Despacho gaussiano documentado.</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48 escenarios convergieron. U entre 0.9368 y 1.0230 pu (limite 0.90-1.10). Cargabilidad max 80.55%. Sin violaciones.</t>
+          <t>72 escenarios convergieron. U entre 0.9363 y 1.0115 pu. Cargabilidad max 80.27%. La condicion critica de subtension es la carga pura, no el caso con proyecto.</t>
         </is>
       </c>
     </row>
@@ -1024,14 +1024,14 @@
           <t>Cortocircuito.py</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMADO: Ikss=0.7146kA en barra propia del generador tras aplicar Ik3PF=238.2A x3 - coincide con lo esperado (714.6A). GD1/GD2 con 'No Short-Circuit Contribution' confirmados en 0 en las demas barras. Falta llenar tabla final vs 10kA</t>
+          <t>Tabla completa de las 16 barras x 3 tipos de falla, sin/con proyecto. Maximo 8.164 kA vs 10 kA de corte -&gt; margen 18%. Secuencia cero validada contra el dato del OR (2.622 kA en 115 kV).</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Perdidas +9.26 kW (2026) / +9.21 kW (2028), concentradas integramente en la linea de evacuacion AL 1.32km. Resto del sistema reduce perdidas.</t>
+          <t>Con despacho horario: el proyecto REDUCE perdidas 2.28 kW (2026) frente a carga pura. Frente al caso base suma 2.51 kW promedio, con horas en que las reduce.</t>
         </is>
       </c>
     </row>
@@ -1152,14 +1152,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>No aplica</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Condicional a los resultados de 6.5.3/6.5.4</t>
+          <t>Sin incumplimientos tecnicos: no hay sobrecargas, ni tensiones fuera de rango, ni superacion de capacidad de corte. No se requieren obras ni evaluacion economica.</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Hora 15: demanda total agregada max. = 8.0269 MW (de Parametros_Demanda.xlsx). Generacion solar = 0 (forzada, sin importar la hora real de sol)</t>
+          <t>Caso de red CargaPura, hora 15 (demanda maxima 8.0269 MW, generacion forzada a 0 en todos los generadores).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Confirmado con datos propios del proyecto</t>
+          <t>Actualizado con el despacho gaussiano (ver seccion Modelacion del despacho de generacion)</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DECISION TOMADA: se usa Hora 11 (maxima generacion real, 564.05 kWh) con su demanda real (7.174 MW agregada).</t>
+          <t>Hora 12: maxima generacion del perfil gaussiano (990 kW proyecto + 660 kW GD1/GD2) con su demanda real de 7.0920 MW.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Confirmado por el usuario</t>
+          <t>Actualizado con el despacho gaussiano (ver seccion Modelacion del despacho de generacion)</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Demanda maxima (6-17): Hora 15 (8.0269 MW). En esa hora la generacion es 390.29 kWh (no es el maximo de generacion, que es la hora 11)</t>
+          <t>Hora 15: maxima demanda (8.0269 MW) con la generacion que corresponde a esa hora segun el perfil (482 kW proyecto).</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mismo tipo de decision que el escenario anterior: usar hora de maxima demanda (15) con su generacion real, en vez de buscar coincidencia exacta que no existe en los datos</t>
+          <t>Actualizado con el despacho gaussiano (ver seccion Modelacion del despacho de generacion)</t>
         </is>
       </c>
     </row>
@@ -1386,14 +1386,14 @@
           <t>Desviacion &gt; 10% entre los calculos del interesado y los del OR (tension, cargabilidad, cortocircuito)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Cumple</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Requiere el calculo de referencia del OR</t>
+          <t>EBSA no entrego resultados de flujo de carga propios. El unico dato de referencia que si entrego (Ik1=2.622 kA en barraje 115 kV) se reproduce exactamente en el modelo. Desviacion interna CasoBase vs con-proyecto: +0.129% en tension.</t>
         </is>
       </c>
     </row>

--- a/informe/Estructura_Informe_Conexion.xlsx
+++ b/informe/Estructura_Informe_Conexion.xlsx
@@ -524,12 +524,16 @@
           <t>Narrativo - se escribe al final con los resultados ya listos</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Falta</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Redactado: antecedentes, alcance, supuestos, tabla resumen de los 6 analisis y conclusion.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1184,12 +1188,16 @@
           <t>Narrativo - se escribe al final</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Falta</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Redactadas: conclusion general, 6 conclusiones por analisis y 6 recomendaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
